--- a/Data/MH_TheRevolt.xlsx
+++ b/Data/MH_TheRevolt.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,881 +472,881 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Who was declared the symbolic leader of the Revolt of 1857?</t>
+          <t>The Revolt of 1857 was also referred to as:</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Civil War</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>War of Religion</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>First War of Indian Independence</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Sepoy Mutiny</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>First War of Indian Independence</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>He was declared the emperor of India by the rebels.</t>
+          <t>Term used by Indian nationalists to honor its significance.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which ruler's state was annexed under the Doctrine of Lapse, triggering her participation in the 1857 revolt?</t>
+          <t>Which of the following social groups was least involved in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Artisans</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Peasants</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Soldiers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Lawyers</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Lawyers</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Her state Jhansi was annexed by the British under the Doctrine of Lapse.</t>
+          <t>They were few and mostly stayed aloof or loyal to the British.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Who led the revolt in Bihar during 1857?</t>
+          <t>The 1857 revolt is considered the first struggle for independence because:</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>It succeeded</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>It united all classes</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>It had nationalist elements</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>It was supported by INC</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>It had nationalist elements</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>A zamindar from Jagdishpur who joined the rebellion despite his age.</t>
+          <t>Though limited, it was the first widespread anti-British effort.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The immediate cause of the 1857 Revolt was related to:</t>
+          <t>Which rebel leader used guerrilla warfare after defeat in open battle?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Heavy taxation</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>New land revenue policies</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Greased cartridges</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Annexation of Awadh</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Greased cartridges</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>The use of animal fat-greased cartridges hurt religious sentiments.</t>
+          <t>He used hit-and-run tactics after initial defeats.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who was the first martyr of the 1857 revolt?</t>
+          <t>The term "sepoy mutiny" was mainly used by:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Nationalist historians</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>British historians</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Marxist historians</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Modern Indian scholars</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>British historians</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>He attacked British officers at Barrackpore.</t>
+          <t>They downplayed the revolt’s scale and called it a mere military rebellion.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which state was annexed by the British on the pretext of misgovernance?</t>
+          <t>Which governor-general annexed most territories before 1857?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Lord Canning</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Satara</t>
+          <t>Lord Wellesley</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Annexed in 1856, seen as an injustice by Indian nobility.</t>
+          <t>He used the Doctrine of Lapse to expand British control.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which of the following was not a cause of the 1857 revolt?</t>
+          <t>Which of the following was promised in the Queen's Proclamation of 1858?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Discrimination in army</t>
+          <t>Right to vote</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>High salary of Indian soldiers</t>
+          <t>Equal rights before law</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Religious interference</t>
+          <t>Complete self-rule</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Annexation policies</t>
+          <t>Independence</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>High salary of Indian soldiers</t>
+          <t>Equal rights before law</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Indian soldiers were paid much less than their British counterparts.</t>
+          <t>It tried to pacify Indians and prevent further revolts.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Who led the revolt in Kanpur?</t>
+          <t>Who was declared the symbolic leader of the Revolt of 1857?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Bahadur Shah Zafar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>Nana Sahib</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Tantia Tope</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Rani Laxmibai</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Tantia Tope</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Kunwar Singh</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>He led the rebellion after being denied his father's pension.</t>
+          <t>He was declared the emperor of India by the rebels.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which female leader actively led troops in the 1857 rebellion?</t>
+          <t>Which book describes the Revolt of 1857 as a national revolt?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Begum Rokeya</t>
+          <t>India’s Struggle for Independence</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>The History of the Indian Mutiny</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>The Indian War of Independence</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Discovery of India</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>The Indian War of Independence</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>She led the revolt in Awadh and resisted British rule.</t>
+          <t>Written by V.D. Savarkar glorifying the revolt.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 was also referred to as:</t>
+          <t>Which of the following best describes the nature of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Civil War</t>
+          <t>Only military</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>War of Religion</t>
+          <t>Only peasant-based</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>First War of Indian Independence</t>
+          <t>Regional uprising</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sepoy Mutiny</t>
+          <t>Combination of political, social, and military causes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>First War of Indian Independence</t>
+          <t>Combination of political, social, and military causes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Term used by Indian nationalists to honor its significance.</t>
+          <t>Multiple classes were involved for various reasons.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which one of these was a British general during the suppression of the revolt?</t>
+          <t>Which princely state supported the British during the 1857 revolt?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Colin Campbell</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Colin Campbell</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>He led the recapture of Lucknow.</t>
+          <t>The Nizam of Hyderabad remained loyal to the British.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which region did not participate in the 1857 revolt?</t>
+          <t>Who captured Delhi back from the rebels in 1857?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Colin Campbell</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>John Nicholson</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Hugh Rose</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>John Nicholson</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Largely stayed loyal to the British due to local rivalries and Sikh-British cooperation.</t>
+          <t>Led British troops to recapture Delhi from Indian rebels.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Who led the revolt in Faizabad?</t>
+          <t>The Revolt of 1857 began from which place?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bahadur Shah</t>
+          <t>Meerut</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Barrackpore</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Meerut</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>An influential religious leader who organized local resistance.</t>
+          <t>It started on May 10, 1857, when soldiers mutinied.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which British policy was resented by Indian rulers leading up to 1857?</t>
+          <t>Which act transferred control from the Company to the Crown?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pitt’s India Act</t>
+          <t>Charter Act 1853</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Subsidiary Alliance</t>
+          <t>Regulating Act</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Doctrine of Lapse</t>
+          <t>Indian Councils Act</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Permanent Settlement</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Doctrine of Lapse</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Used to annex several princely states without heirs.</t>
+          <t>Ended the East India Company's rule.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which book describes the Revolt of 1857 as a national revolt?</t>
+          <t>Which of the following was not a cause of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India’s Struggle for Independence</t>
+          <t>Discrimination in army</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>The History of the Indian Mutiny</t>
+          <t>High salary of Indian soldiers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>The Indian War of Independence</t>
+          <t>Religious interference</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Discovery of India</t>
+          <t>Annexation policies</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>The Indian War of Independence</t>
+          <t>High salary of Indian soldiers</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Written by V.D. Savarkar glorifying the revolt.</t>
+          <t>Indian soldiers were paid much less than their British counterparts.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What was the main reason behind the failure of the 1857 revolt?</t>
+          <t>Which female leader actively led troops in the 1857 rebellion?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>British military strength</t>
+          <t>Begum Rokeya</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lack of foreign support</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lack of leadership and unity</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Economic weakness</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lack of leadership and unity</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>There was no single coordinated command structure.</t>
+          <t>She led the revolt in Awadh and resisted British rule.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who among the following was hanged in 1859 for his role in the revolt?</t>
+          <t>Which of these regions remained largely unaffected by the revolt?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bahadur Shah</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>He was captured and executed by the British.</t>
+          <t>Many local rulers, especially Sikhs, supported the British.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which of the following was a social cause of the 1857 revolt?</t>
+          <t>Which leader used religious appeal to mobilize people in 1857?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ban on widow remarriage</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Introduction of western education</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sati abolition</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Religious interference by British</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Religious interference by British</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Missionary activities and law reforms hurt native sentiments.</t>
+          <t>He used Islamic preaching to unite fighters in Awadh.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who was the British Governor-General during the revolt?</t>
+          <t>Which of the following was a social cause of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lord Canning</t>
+          <t>Ban on widow remarriage</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>Introduction of western education</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>Sati abolition</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Religious interference by British</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lord Canning</t>
+          <t>Religious interference by British</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>He was the last Governor-General of the East India Company and first Viceroy of British India.</t>
+          <t>Missionary activities and law reforms hurt native sentiments.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which city saw fierce fighting and massacre during the revolt?</t>
+          <t>The immediate cause of the 1857 Revolt was related to:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Heavy taxation</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>New land revenue policies</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Greased cartridges</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Annexation of Awadh</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Greased cartridges</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Site of Nana Sahib’s major rebellion and British retaliation.</t>
+          <t>The use of animal fat-greased cartridges hurt religious sentiments.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which of the following pairs is correctly matched?</t>
+          <t>What was the result of the revolt of 1857?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lucknow – Rani Laxmibai</t>
+          <t>British left India</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Kanpur – Tantia Tope</t>
+          <t>Company rule ended</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Delhi – Bahadur Shah Zafar</t>
+          <t>Indian National Congress formed</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jhansi – Nana Sahib</t>
+          <t>Queen Victoria exiled</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Delhi – Bahadur Shah Zafar</t>
+          <t>Company rule ended</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>He was declared the emperor in Delhi by the rebels.</t>
+          <t>The British Crown took direct control over India in 1858.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What was the result of the revolt of 1857?</t>
+          <t>Which ruler's state was annexed under the Doctrine of Lapse, triggering her participation in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>British left India</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Company rule ended</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Indian National Congress formed</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Queen Victoria exiled</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Company rule ended</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>The British Crown took direct control over India in 1858.</t>
+          <t>Her state Jhansi was annexed by the British under the Doctrine of Lapse.</t>
         </is>
       </c>
     </row>
@@ -1392,561 +1392,561 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which famous queen died in battle during the 1857 revolt?</t>
+          <t>The Revolt of 1857 was described as a "feudal outburst" by:</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rani Velu Nachiyar</t>
+          <t>Bipan Chandra</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>R.C. Majumdar</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Karl Marx</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rani Durgavati</t>
+          <t>James Mill</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Karl Marx</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Fought bravely against the British in Gwalior.</t>
+          <t>He called it a rebellion of feudal lords against modern capitalism.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Who captured Delhi back from the rebels in 1857?</t>
+          <t>Which region did not participate in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Colin Campbell</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>John Nicholson</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hugh Rose</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>John Nicholson</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Led British troops to recapture Delhi from Indian rebels.</t>
+          <t>Largely stayed loyal to the British due to local rivalries and Sikh-British cooperation.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What was the main military grievance that triggered the Revolt of 1857?</t>
+          <t>What was the role of Bahadur Shah Zafar in the revolt?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lack of promotion</t>
+          <t>Military planner</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Low salary</t>
+          <t>Active field commander</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Use of greased cartridges</t>
+          <t>Symbolic leader</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deployment in Burma</t>
+          <t>British spy</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Use of greased cartridges</t>
+          <t>Symbolic leader</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Cartridges greased with cow/pig fat offended both Hindus and Muslims.</t>
+          <t>He was declared the emperor by the rebels, though old and powerless.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which one of the following cities was not a major centre of the 1857 revolt?</t>
+          <t>Which group played a limited role in the revolt of 1857?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Peasants</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Zamindars</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Princes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Western-educated Indians</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Western-educated Indians</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Southern India remained mostly unaffected by the revolt.</t>
+          <t>They generally stayed loyal or neutral, as they benefited from British reforms.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Who among the following led the revolt at Gwalior?</t>
+          <t>The 1857 revolt failed largely due to:</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Lack of weapons</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Lack of local support</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Limited area of spread</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Strong leadership</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Limited area of spread</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>He continued the struggle after Rani Laxmibai's death.</t>
+          <t>It did not involve most of South and East India.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which one of the following was a consequence of the 1857 revolt?</t>
+          <t>Who described the revolt as “a war between civilization and barbarism”?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indian National Congress was formed</t>
+          <t>James Mill</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>End of Company rule</t>
+          <t>Winston Churchill</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Beginning of Non-cooperation</t>
+          <t>Thomas Macaulay</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>End of Company rule</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>The British Crown took direct control over India in 1858.</t>
+          <t>British leaders used such language to justify colonialism.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Which rebel leader used guerrilla warfare after defeat in open battle?</t>
+          <t>What was the main military grievance that triggered the Revolt of 1857?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Lack of promotion</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Low salary</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Use of greased cartridges</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Deployment in Burma</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Use of greased cartridges</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>He used hit-and-run tactics after initial defeats.</t>
+          <t>Cartridges greased with cow/pig fat offended both Hindus and Muslims.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which of the following was not a leader in the 1857 revolt?</t>
+          <t>What was the main reason behind the failure of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>British military strength</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Rani Gaidinliu</t>
+          <t>Lack of foreign support</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Lack of leadership and unity</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Economic weakness</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rani Gaidinliu</t>
+          <t>Lack of leadership and unity</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>She was a Naga leader who resisted the British in the 1930s, not 1857.</t>
+          <t>There was no single coordinated command structure.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What was the role of Bahadur Shah Zafar in the revolt?</t>
+          <t>Which city saw fierce fighting and massacre during the revolt?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Military planner</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Active field commander</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Symbolic leader</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>British spy</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Symbolic leader</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>He was declared the emperor by the rebels, though old and powerless.</t>
+          <t>Site of Nana Sahib’s major rebellion and British retaliation.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which princely state supported the British during the 1857 revolt?</t>
+          <t>Who led the revolt in Bihar during 1857?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>The Nizam of Hyderabad remained loyal to the British.</t>
+          <t>A zamindar from Jagdishpur who joined the rebellion despite his age.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The 1857 revolt is considered the first struggle for independence because:</t>
+          <t>Which of the following was not a leader in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>It succeeded</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>It united all classes</t>
+          <t>Rani Gaidinliu</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>It had nationalist elements</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>It was supported by INC</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>It had nationalist elements</t>
+          <t>Rani Gaidinliu</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Though limited, it was the first widespread anti-British effort.</t>
+          <t>She was a Naga leader who resisted the British in the 1930s, not 1857.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which of these regions remained largely unaffected by the revolt?</t>
+          <t>Who was the first martyr of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Many local rulers, especially Sikhs, supported the British.</t>
+          <t>He attacked British officers at Barrackpore.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who described the revolt as “a war between civilization and barbarism”?</t>
+          <t>Which one of the following was a consequence of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>James Mill</t>
+          <t>Indian National Congress was formed</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Winston Churchill</t>
+          <t>End of Company rule</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Thomas Macaulay</t>
+          <t>Beginning of Non-cooperation</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>End of Company rule</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>British leaders used such language to justify colonialism.</t>
+          <t>The British Crown took direct control over India in 1858.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The 1857 revolt failed largely due to:</t>
+          <t>Which British policy was resented by Indian rulers leading up to 1857?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lack of weapons</t>
+          <t>Pitt’s India Act</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lack of local support</t>
+          <t>Subsidiary Alliance</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Limited area of spread</t>
+          <t>Doctrine of Lapse</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Strong leadership</t>
+          <t>Permanent Settlement</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Limited area of spread</t>
+          <t>Doctrine of Lapse</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>It did not involve most of South and East India.</t>
+          <t>Used to annex several princely states without heirs.</t>
         </is>
       </c>
     </row>
@@ -1956,127 +1956,127 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which group played a limited role in the revolt of 1857?</t>
+          <t>Who led the revolt in Faizabad?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Peasants</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Zamindars</t>
+          <t>Bahadur Shah</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Princes</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Western-educated Indians</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Western-educated Indians</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>They generally stayed loyal or neutral, as they benefited from British reforms.</t>
+          <t>An influential religious leader who organized local resistance.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which of these was not a cause of discontent among Indian soldiers?</t>
+          <t>Which of the following pairs is correctly matched?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Restriction on caste practices</t>
+          <t>Lucknow – Rani Laxmibai</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Deployment overseas</t>
+          <t>Kanpur – Tantia Tope</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Equal pay with British troops</t>
+          <t>Delhi – Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Religious interference</t>
+          <t>Jhansi – Nana Sahib</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Equal pay with British troops</t>
+          <t>Delhi – Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>They were paid **less**, not equally.</t>
+          <t>He was declared the emperor in Delhi by the rebels.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>After the 1857 revolt, the British introduced:</t>
+          <t>Which one of these was a British general during the suppression of the revolt?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Colin Campbell</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Queen’s Proclamation</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Judicial system</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Queen’s Proclamation</t>
+          <t>Colin Campbell</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>It promised non-interference in religion and equal protection of law.</t>
+          <t>He led the recapture of Lucknow.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which leader used religious appeal to mobilize people in 1857?</t>
+          <t>Who led the revolt in Kanpur?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2086,27 +2086,27 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>Tantia Tope</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>Kunwar Singh</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Rani Laxmibai</t>
-        </is>
-      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>He used Islamic preaching to unite fighters in Awadh.</t>
+          <t>He led the rebellion after being denied his father's pension.</t>
         </is>
       </c>
     </row>
@@ -2116,47 +2116,47 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The term "sepoy mutiny" was mainly used by:</t>
+          <t>Who among the following was hanged in 1859 for his role in the revolt?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nationalist historians</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>British historians</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Marxist historians</t>
+          <t>Bahadur Shah</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Modern Indian scholars</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>British historians</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>They downplayed the revolt’s scale and called it a mere military rebellion.</t>
+          <t>He was captured and executed by the British.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 began from which place?</t>
+          <t>Which one of the following cities was not a major centre of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2166,237 +2166,237 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Meerut</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>Madras</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>Kanpur</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Barrackpore</t>
-        </is>
-      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Meerut</t>
+          <t>Madras</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>It started on May 10, 1857, when soldiers mutinied.</t>
+          <t>Southern India remained mostly unaffected by the revolt.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which act transferred control from the Company to the Crown?</t>
+          <t>The Revolt of 1857 is also known in British records as:</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charter Act 1853</t>
+          <t>Mutiny of 1857</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Regulating Act</t>
+          <t>Civil Rebellion</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Indian Councils Act</t>
+          <t>Indian Freedom War</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Sepoy Rebellion</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Mutiny of 1857</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ended the East India Company's rule.</t>
+          <t>Official British term used to minimize its impact.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 is also known in British records as:</t>
+          <t>Which famous queen died in battle during the 1857 revolt?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mutiny of 1857</t>
+          <t>Rani Velu Nachiyar</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Civil Rebellion</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Indian Freedom War</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sepoy Rebellion</t>
+          <t>Rani Durgavati</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mutiny of 1857</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Official British term used to minimize its impact.</t>
+          <t>Fought bravely against the British in Gwalior.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which of the following best describes the nature of the 1857 revolt?</t>
+          <t>After the 1857 revolt, the British introduced:</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Only military</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Only peasant-based</t>
+          <t>Queen’s Proclamation</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Regional uprising</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Combination of political, social, and military causes</t>
+          <t>Judicial system</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Combination of political, social, and military causes</t>
+          <t>Queen’s Proclamation</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Multiple classes were involved for various reasons.</t>
+          <t>It promised non-interference in religion and equal protection of law.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which of the following social groups was least involved in the 1857 revolt?</t>
+          <t>Which state was annexed by the British on the pretext of misgovernance?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Artisans</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Peasants</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Soldiers</t>
+          <t>Satara</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lawyers</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lawyers</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>They were few and mostly stayed aloof or loyal to the British.</t>
+          <t>Annexed in 1856, seen as an injustice by Indian nobility.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which of the following was promised in the Queen's Proclamation of 1858?</t>
+          <t>Which of these was not a cause of discontent among Indian soldiers?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Right to vote</t>
+          <t>Restriction on caste practices</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Equal rights before law</t>
+          <t>Deployment overseas</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Complete self-rule</t>
+          <t>Equal pay with British troops</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Independence</t>
+          <t>Religious interference</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Equal rights before law</t>
+          <t>Equal pay with British troops</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>It tried to pacify Indians and prevent further revolts.</t>
+          <t>They were paid **less**, not equally.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which governor-general annexed most territories before 1857?</t>
+          <t>Who was the British Governor-General during the revolt?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lord Wellesley</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2421,52 +2421,52 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>Lord Canning</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>He used the Doctrine of Lapse to expand British control.</t>
+          <t>He was the last Governor-General of the East India Company and first Viceroy of British India.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 was described as a "feudal outburst" by:</t>
+          <t>Who among the following led the revolt at Gwalior?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bipan Chandra</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>R.C. Majumdar</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Karl Marx</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>James Mill</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Karl Marx</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>He called it a rebellion of feudal lords against modern capitalism.</t>
+          <t>He continued the struggle after Rani Laxmibai's death.</t>
         </is>
       </c>
     </row>

--- a/Data/MH_TheRevolt.xlsx
+++ b/Data/MH_TheRevolt.xlsx
@@ -472,81 +472,81 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 was also referred to as:</t>
+          <t>Which region did not participate in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Civil War</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>War of Religion</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>First War of Indian Independence</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sepoy Mutiny</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>First War of Indian Independence</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Term used by Indian nationalists to honor its significance.</t>
+          <t>Largely stayed loyal to the British due to local rivalries and Sikh-British cooperation.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which of the following social groups was least involved in the 1857 revolt?</t>
+          <t>Which of the following best describes the nature of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Artisans</t>
+          <t>Only military</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Peasants</t>
+          <t>Only peasant-based</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Soldiers</t>
+          <t>Regional uprising</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lawyers</t>
+          <t>Combination of political, social, and military causes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lawyers</t>
+          <t>Combination of political, social, and military causes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>They were few and mostly stayed aloof or loyal to the British.</t>
+          <t>Multiple classes were involved for various reasons.</t>
         </is>
       </c>
     </row>
@@ -556,77 +556,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The 1857 revolt is considered the first struggle for independence because:</t>
+          <t>Which female leader actively led troops in the 1857 rebellion?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>It succeeded</t>
+          <t>Begum Rokeya</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>It united all classes</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>It had nationalist elements</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>It was supported by INC</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>It had nationalist elements</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Though limited, it was the first widespread anti-British effort.</t>
+          <t>She led the revolt in Awadh and resisted British rule.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which rebel leader used guerrilla warfare after defeat in open battle?</t>
+          <t>The Revolt of 1857 was also referred to as:</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Civil War</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>War of Religion</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>First War of Indian Independence</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Sepoy Mutiny</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>First War of Indian Independence</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>He used hit-and-run tactics after initial defeats.</t>
+          <t>Term used by Indian nationalists to honor its significance.</t>
         </is>
       </c>
     </row>
@@ -672,251 +672,251 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which governor-general annexed most territories before 1857?</t>
+          <t>Who described the revolt as “a war between civilization and barbarism”?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lord Canning</t>
+          <t>James Mill</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lord Wellesley</t>
+          <t>Winston Churchill</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Thomas Macaulay</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>He used the Doctrine of Lapse to expand British control.</t>
+          <t>British leaders used such language to justify colonialism.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which of the following was promised in the Queen's Proclamation of 1858?</t>
+          <t>Who led the revolt in Bihar during 1857?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Right to vote</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Equal rights before law</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Complete self-rule</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Independence</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Equal rights before law</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>It tried to pacify Indians and prevent further revolts.</t>
+          <t>A zamindar from Jagdishpur who joined the rebellion despite his age.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Who was declared the symbolic leader of the Revolt of 1857?</t>
+          <t>Which of the following was not a cause of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Discrimination in army</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>High salary of Indian soldiers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Religious interference</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Annexation policies</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>High salary of Indian soldiers</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>He was declared the emperor of India by the rebels.</t>
+          <t>Indian soldiers were paid much less than their British counterparts.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which book describes the Revolt of 1857 as a national revolt?</t>
+          <t>Who was the first martyr of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>India’s Struggle for Independence</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>The History of the Indian Mutiny</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>The Indian War of Independence</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Discovery of India</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>The Indian War of Independence</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Written by V.D. Savarkar glorifying the revolt.</t>
+          <t>He attacked British officers at Barrackpore.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which of the following best describes the nature of the 1857 revolt?</t>
+          <t>The 1857 revolt is considered the first struggle for independence because:</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Only military</t>
+          <t>It succeeded</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Only peasant-based</t>
+          <t>It united all classes</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Regional uprising</t>
+          <t>It had nationalist elements</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Combination of political, social, and military causes</t>
+          <t>It was supported by INC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Combination of political, social, and military causes</t>
+          <t>It had nationalist elements</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Multiple classes were involved for various reasons.</t>
+          <t>Though limited, it was the first widespread anti-British effort.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which princely state supported the British during the 1857 revolt?</t>
+          <t>Who led the revolt in Faizabad?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Bahadur Shah</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>The Nizam of Hyderabad remained loyal to the British.</t>
+          <t>An influential religious leader who organized local resistance.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Who captured Delhi back from the rebels in 1857?</t>
+          <t>Which one of these was a British general during the suppression of the revolt?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -926,932 +926,932 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>John Nicholson</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hugh Rose</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>John Nicholson</t>
+          <t>Colin Campbell</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Led British troops to recapture Delhi from Indian rebels.</t>
+          <t>He led the recapture of Lucknow.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 began from which place?</t>
+          <t>After the 1857 revolt, the British introduced:</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Meerut</t>
+          <t>Queen’s Proclamation</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barrackpore</t>
+          <t>Judicial system</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Meerut</t>
+          <t>Queen’s Proclamation</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>It started on May 10, 1857, when soldiers mutinied.</t>
+          <t>It promised non-interference in religion and equal protection of law.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which act transferred control from the Company to the Crown?</t>
+          <t>Who among the following led the revolt at Gwalior?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Charter Act 1853</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Regulating Act</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Indian Councils Act</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Ended the East India Company's rule.</t>
+          <t>He continued the struggle after Rani Laxmibai's death.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which of the following was not a cause of the 1857 revolt?</t>
+          <t>The Revolt of 1857 is also known in British records as:</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Discrimination in army</t>
+          <t>Mutiny of 1857</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>High salary of Indian soldiers</t>
+          <t>Civil Rebellion</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Religious interference</t>
+          <t>Indian Freedom War</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Annexation policies</t>
+          <t>Sepoy Rebellion</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>High salary of Indian soldiers</t>
+          <t>Mutiny of 1857</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Indian soldiers were paid much less than their British counterparts.</t>
+          <t>Official British term used to minimize its impact.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which female leader actively led troops in the 1857 rebellion?</t>
+          <t>What was the main military grievance that triggered the Revolt of 1857?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Begum Rokeya</t>
+          <t>Lack of promotion</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Low salary</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Use of greased cartridges</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Deployment in Burma</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Use of greased cartridges</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>She led the revolt in Awadh and resisted British rule.</t>
+          <t>Cartridges greased with cow/pig fat offended both Hindus and Muslims.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which of these regions remained largely unaffected by the revolt?</t>
+          <t>Who was declared the symbolic leader of the Revolt of 1857?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Many local rulers, especially Sikhs, supported the British.</t>
+          <t>He was declared the emperor of India by the rebels.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which leader used religious appeal to mobilize people in 1857?</t>
+          <t>Which of the following was promised in the Queen's Proclamation of 1858?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Right to vote</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Equal rights before law</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Complete self-rule</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Independence</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Equal rights before law</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>He used Islamic preaching to unite fighters in Awadh.</t>
+          <t>It tried to pacify Indians and prevent further revolts.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which of the following was a social cause of the 1857 revolt?</t>
+          <t>Who among the following was hanged in 1859 for his role in the revolt?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ban on widow remarriage</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Introduction of western education</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sati abolition</t>
+          <t>Bahadur Shah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Religious interference by British</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Religious interference by British</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Missionary activities and law reforms hurt native sentiments.</t>
+          <t>He was captured and executed by the British.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The immediate cause of the 1857 Revolt was related to:</t>
+          <t>Which British policy was resented by Indian rulers leading up to 1857?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Heavy taxation</t>
+          <t>Pitt’s India Act</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>New land revenue policies</t>
+          <t>Subsidiary Alliance</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Greased cartridges</t>
+          <t>Doctrine of Lapse</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Annexation of Awadh</t>
+          <t>Permanent Settlement</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Greased cartridges</t>
+          <t>Doctrine of Lapse</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The use of animal fat-greased cartridges hurt religious sentiments.</t>
+          <t>Used to annex several princely states without heirs.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What was the result of the revolt of 1857?</t>
+          <t>Which of these was not a cause of discontent among Indian soldiers?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>British left India</t>
+          <t>Restriction on caste practices</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Company rule ended</t>
+          <t>Deployment overseas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Indian National Congress formed</t>
+          <t>Equal pay with British troops</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Queen Victoria exiled</t>
+          <t>Religious interference</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Company rule ended</t>
+          <t>Equal pay with British troops</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>The British Crown took direct control over India in 1858.</t>
+          <t>They were paid **less**, not equally.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which ruler's state was annexed under the Doctrine of Lapse, triggering her participation in the 1857 revolt?</t>
+          <t>Which state was annexed by the British on the pretext of misgovernance?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Satara</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Her state Jhansi was annexed by the British under the Doctrine of Lapse.</t>
+          <t>Annexed in 1856, seen as an injustice by Indian nobility.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who among the following called the revolt a ‘sepoy mutiny’?</t>
+          <t>What was the role of Bahadur Shah Zafar in the revolt?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Military planner</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>R.C. Majumdar</t>
+          <t>Active field commander</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>Symbolic leader</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>James Mill</t>
+          <t>British spy</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>R.C. Majumdar</t>
+          <t>Symbolic leader</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>He considered it a limited military uprising, not a national movement.</t>
+          <t>He was declared the emperor by the rebels, though old and powerless.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 was described as a "feudal outburst" by:</t>
+          <t>Who led the revolt in Kanpur?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bipan Chandra</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>R.C. Majumdar</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Karl Marx</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>James Mill</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Karl Marx</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>He called it a rebellion of feudal lords against modern capitalism.</t>
+          <t>He led the rebellion after being denied his father's pension.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which region did not participate in the 1857 revolt?</t>
+          <t>Which famous queen died in battle during the 1857 revolt?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rani Velu Nachiyar</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Rani Durgavati</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Largely stayed loyal to the British due to local rivalries and Sikh-British cooperation.</t>
+          <t>Fought bravely against the British in Gwalior.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What was the role of Bahadur Shah Zafar in the revolt?</t>
+          <t>Which ruler's state was annexed under the Doctrine of Lapse, triggering her participation in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Military planner</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Active field commander</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Symbolic leader</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>British spy</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Symbolic leader</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>He was declared the emperor by the rebels, though old and powerless.</t>
+          <t>Her state Jhansi was annexed by the British under the Doctrine of Lapse.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which group played a limited role in the revolt of 1857?</t>
+          <t>The Revolt of 1857 began from which place?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Peasants</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Zamindars</t>
+          <t>Meerut</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Princes</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Western-educated Indians</t>
+          <t>Barrackpore</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Western-educated Indians</t>
+          <t>Meerut</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>They generally stayed loyal or neutral, as they benefited from British reforms.</t>
+          <t>It started on May 10, 1857, when soldiers mutinied.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The 1857 revolt failed largely due to:</t>
+          <t>Which princely state supported the British during the 1857 revolt?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lack of weapons</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lack of local support</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Limited area of spread</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Strong leadership</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Limited area of spread</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>It did not involve most of South and East India.</t>
+          <t>The Nizam of Hyderabad remained loyal to the British.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Who described the revolt as “a war between civilization and barbarism”?</t>
+          <t>Which group played a limited role in the revolt of 1857?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>James Mill</t>
+          <t>Peasants</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>Zamindars</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Winston Churchill</t>
+          <t>Princes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Thomas Macaulay</t>
+          <t>Western-educated Indians</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>Western-educated Indians</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>British leaders used such language to justify colonialism.</t>
+          <t>They generally stayed loyal or neutral, as they benefited from British reforms.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What was the main military grievance that triggered the Revolt of 1857?</t>
+          <t>Which governor-general annexed most territories before 1857?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lack of promotion</t>
+          <t>Lord Canning</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Low salary</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Use of greased cartridges</t>
+          <t>Lord Wellesley</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Deployment in Burma</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Use of greased cartridges</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Cartridges greased with cow/pig fat offended both Hindus and Muslims.</t>
+          <t>He used the Doctrine of Lapse to expand British control.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What was the main reason behind the failure of the 1857 revolt?</t>
+          <t>Which book describes the Revolt of 1857 as a national revolt?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>British military strength</t>
+          <t>India’s Struggle for Independence</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Lack of foreign support</t>
+          <t>The History of the Indian Mutiny</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lack of leadership and unity</t>
+          <t>The Indian War of Independence</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Economic weakness</t>
+          <t>Discovery of India</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lack of leadership and unity</t>
+          <t>The Indian War of Independence</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>There was no single coordinated command structure.</t>
+          <t>Written by V.D. Savarkar glorifying the revolt.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which city saw fierce fighting and massacre during the revolt?</t>
+          <t>Which one of the following cities was not a major centre of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Madras</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Kanpur</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Amritsar</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Hyderabad</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Madras</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Site of Nana Sahib’s major rebellion and British retaliation.</t>
+          <t>Southern India remained mostly unaffected by the revolt.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Who led the revolt in Bihar during 1857?</t>
+          <t>Which city saw fierce fighting and massacre during the revolt?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>A zamindar from Jagdishpur who joined the rebellion despite his age.</t>
+          <t>Site of Nana Sahib’s major rebellion and British retaliation.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which of the following was not a leader in the 1857 revolt?</t>
+          <t>Which of these regions remained largely unaffected by the revolt?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Rani Gaidinliu</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rani Gaidinliu</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>She was a Naga leader who resisted the British in the 1930s, not 1857.</t>
+          <t>Many local rulers, especially Sikhs, supported the British.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Who was the first martyr of the 1857 revolt?</t>
+          <t>Which of the following was not a leader in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Rani Gaidinliu</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1861,612 +1861,612 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Rani Gaidinliu</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>He attacked British officers at Barrackpore.</t>
+          <t>She was a Naga leader who resisted the British in the 1930s, not 1857.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Which one of the following was a consequence of the 1857 revolt?</t>
+          <t>The 1857 revolt failed largely due to:</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Indian National Congress was formed</t>
+          <t>Lack of weapons</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Lack of local support</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>End of Company rule</t>
+          <t>Limited area of spread</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Beginning of Non-cooperation</t>
+          <t>Strong leadership</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>End of Company rule</t>
+          <t>Limited area of spread</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>The British Crown took direct control over India in 1858.</t>
+          <t>It did not involve most of South and East India.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which British policy was resented by Indian rulers leading up to 1857?</t>
+          <t>Which of the following was a social cause of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pitt’s India Act</t>
+          <t>Ban on widow remarriage</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Subsidiary Alliance</t>
+          <t>Introduction of western education</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Doctrine of Lapse</t>
+          <t>Sati abolition</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Permanent Settlement</t>
+          <t>Religious interference by British</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Doctrine of Lapse</t>
+          <t>Religious interference by British</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Used to annex several princely states without heirs.</t>
+          <t>Missionary activities and law reforms hurt native sentiments.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who led the revolt in Faizabad?</t>
+          <t>What was the main reason behind the failure of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>British military strength</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Bahadur Shah</t>
+          <t>Lack of foreign support</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Lack of leadership and unity</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Economic weakness</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Lack of leadership and unity</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>An influential religious leader who organized local resistance.</t>
+          <t>There was no single coordinated command structure.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which of the following pairs is correctly matched?</t>
+          <t>What was the result of the revolt of 1857?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lucknow – Rani Laxmibai</t>
+          <t>British left India</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Kanpur – Tantia Tope</t>
+          <t>Company rule ended</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Delhi – Bahadur Shah Zafar</t>
+          <t>Indian National Congress formed</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jhansi – Nana Sahib</t>
+          <t>Queen Victoria exiled</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Delhi – Bahadur Shah Zafar</t>
+          <t>Company rule ended</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>He was declared the emperor in Delhi by the rebels.</t>
+          <t>The British Crown took direct control over India in 1858.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which one of these was a British general during the suppression of the revolt?</t>
+          <t>Which act transferred control from the Company to the Crown?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Colin Campbell</t>
+          <t>Charter Act 1853</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Regulating Act</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Indian Councils Act</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Colin Campbell</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>He led the recapture of Lucknow.</t>
+          <t>Ended the East India Company's rule.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who led the revolt in Kanpur?</t>
+          <t>Who among the following called the revolt a ‘sepoy mutiny’?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>R.C. Majumdar</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>James Mill</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>R.C. Majumdar</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>He led the rebellion after being denied his father's pension.</t>
+          <t>He considered it a limited military uprising, not a national movement.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Who among the following was hanged in 1859 for his role in the revolt?</t>
+          <t>Who captured Delhi back from the rebels in 1857?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Colin Campbell</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>John Nicholson</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bahadur Shah</t>
+          <t>Hugh Rose</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>John Nicholson</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>He was captured and executed by the British.</t>
+          <t>Led British troops to recapture Delhi from Indian rebels.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which one of the following cities was not a major centre of the 1857 revolt?</t>
+          <t>Which rebel leader used guerrilla warfare after defeat in open battle?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Southern India remained mostly unaffected by the revolt.</t>
+          <t>He used hit-and-run tactics after initial defeats.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 is also known in British records as:</t>
+          <t>Which leader used religious appeal to mobilize people in 1857?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mutiny of 1857</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Civil Rebellion</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Indian Freedom War</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sepoy Rebellion</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Mutiny of 1857</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Official British term used to minimize its impact.</t>
+          <t>He used Islamic preaching to unite fighters in Awadh.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which famous queen died in battle during the 1857 revolt?</t>
+          <t>Who was the British Governor-General during the revolt?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rani Velu Nachiyar</t>
+          <t>Lord Canning</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rani Durgavati</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Lord Canning</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fought bravely against the British in Gwalior.</t>
+          <t>He was the last Governor-General of the East India Company and first Viceroy of British India.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>After the 1857 revolt, the British introduced:</t>
+          <t>Which of the following pairs is correctly matched?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Lucknow – Rani Laxmibai</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Queen’s Proclamation</t>
+          <t>Kanpur – Tantia Tope</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Delhi – Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Judicial system</t>
+          <t>Jhansi – Nana Sahib</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Queen’s Proclamation</t>
+          <t>Delhi – Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>It promised non-interference in religion and equal protection of law.</t>
+          <t>He was declared the emperor in Delhi by the rebels.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which state was annexed by the British on the pretext of misgovernance?</t>
+          <t>The Revolt of 1857 was described as a "feudal outburst" by:</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Bipan Chandra</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>R.C. Majumdar</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Satara</t>
+          <t>Karl Marx</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>James Mill</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Karl Marx</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Annexed in 1856, seen as an injustice by Indian nobility.</t>
+          <t>He called it a rebellion of feudal lords against modern capitalism.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which of these was not a cause of discontent among Indian soldiers?</t>
+          <t>Which one of the following was a consequence of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Restriction on caste practices</t>
+          <t>Indian National Congress was formed</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Deployment overseas</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Equal pay with British troops</t>
+          <t>End of Company rule</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Religious interference</t>
+          <t>Beginning of Non-cooperation</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Equal pay with British troops</t>
+          <t>End of Company rule</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>They were paid **less**, not equally.</t>
+          <t>The British Crown took direct control over India in 1858.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who was the British Governor-General during the revolt?</t>
+          <t>The immediate cause of the 1857 Revolt was related to:</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lord Canning</t>
+          <t>Heavy taxation</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>New land revenue policies</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>Greased cartridges</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Annexation of Awadh</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lord Canning</t>
+          <t>Greased cartridges</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>He was the last Governor-General of the East India Company and first Viceroy of British India.</t>
+          <t>The use of animal fat-greased cartridges hurt religious sentiments.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Who among the following led the revolt at Gwalior?</t>
+          <t>Which of the following social groups was least involved in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Artisans</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Peasants</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Soldiers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Lawyers</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Lawyers</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>He continued the struggle after Rani Laxmibai's death.</t>
+          <t>They were few and mostly stayed aloof or loyal to the British.</t>
         </is>
       </c>
     </row>

--- a/Data/MH_TheRevolt.xlsx
+++ b/Data/MH_TheRevolt.xlsx
@@ -472,1161 +472,1161 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which region did not participate in the 1857 revolt?</t>
+          <t>Which princely state supported the British during the 1857 revolt?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Largely stayed loyal to the British due to local rivalries and Sikh-British cooperation.</t>
+          <t>The Nizam of Hyderabad remained loyal to the British.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which of the following best describes the nature of the 1857 revolt?</t>
+          <t>Which of the following was promised in the Queen's Proclamation of 1858?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Only military</t>
+          <t>Right to vote</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Only peasant-based</t>
+          <t>Equal rights before law</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Regional uprising</t>
+          <t>Complete self-rule</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Combination of political, social, and military causes</t>
+          <t>Independence</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Combination of political, social, and military causes</t>
+          <t>Equal rights before law</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Multiple classes were involved for various reasons.</t>
+          <t>It tried to pacify Indians and prevent further revolts.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which female leader actively led troops in the 1857 rebellion?</t>
+          <t>Who captured Delhi back from the rebels in 1857?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Begum Rokeya</t>
+          <t>Colin Campbell</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>John Nicholson</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Hugh Rose</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>John Nicholson</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>She led the revolt in Awadh and resisted British rule.</t>
+          <t>Led British troops to recapture Delhi from Indian rebels.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 was also referred to as:</t>
+          <t>Which state was annexed by the British on the pretext of misgovernance?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Civil War</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>War of Religion</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>First War of Indian Independence</t>
+          <t>Satara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sepoy Mutiny</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>First War of Indian Independence</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Term used by Indian nationalists to honor its significance.</t>
+          <t>Annexed in 1856, seen as an injustice by Indian nobility.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The term "sepoy mutiny" was mainly used by:</t>
+          <t>Which rebel leader used guerrilla warfare after defeat in open battle?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nationalist historians</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>British historians</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Marxist historians</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Modern Indian scholars</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>British historians</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>They downplayed the revolt’s scale and called it a mere military rebellion.</t>
+          <t>He used hit-and-run tactics after initial defeats.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who described the revolt as “a war between civilization and barbarism”?</t>
+          <t>Which of the following best describes the nature of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>James Mill</t>
+          <t>Only military</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>Only peasant-based</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Winston Churchill</t>
+          <t>Regional uprising</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomas Macaulay</t>
+          <t>Combination of political, social, and military causes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>Combination of political, social, and military causes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>British leaders used such language to justify colonialism.</t>
+          <t>Multiple classes were involved for various reasons.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Who led the revolt in Bihar during 1857?</t>
+          <t>Which group played a limited role in the revolt of 1857?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Peasants</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Zamindars</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Princes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Western-educated Indians</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Western-educated Indians</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>A zamindar from Jagdishpur who joined the rebellion despite his age.</t>
+          <t>They generally stayed loyal or neutral, as they benefited from British reforms.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which of the following was not a cause of the 1857 revolt?</t>
+          <t>Who was the first martyr of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Discrimination in army</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>High salary of Indian soldiers</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Religious interference</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Annexation policies</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>High salary of Indian soldiers</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Indian soldiers were paid much less than their British counterparts.</t>
+          <t>He attacked British officers at Barrackpore.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Who was the first martyr of the 1857 revolt?</t>
+          <t>Which one of the following cities was not a major centre of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Madras</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Madras</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>He attacked British officers at Barrackpore.</t>
+          <t>Southern India remained mostly unaffected by the revolt.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The 1857 revolt is considered the first struggle for independence because:</t>
+          <t>Which famous queen died in battle during the 1857 revolt?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>It succeeded</t>
+          <t>Rani Velu Nachiyar</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>It united all classes</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>It had nationalist elements</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>It was supported by INC</t>
+          <t>Rani Durgavati</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>It had nationalist elements</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Though limited, it was the first widespread anti-British effort.</t>
+          <t>Fought bravely against the British in Gwalior.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Who led the revolt in Faizabad?</t>
+          <t>Which of the following pairs is correctly matched?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Lucknow – Rani Laxmibai</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bahadur Shah</t>
+          <t>Kanpur – Tantia Tope</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Delhi – Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Jhansi – Nana Sahib</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Delhi – Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>An influential religious leader who organized local resistance.</t>
+          <t>He was declared the emperor in Delhi by the rebels.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which one of these was a British general during the suppression of the revolt?</t>
+          <t>Which female leader actively led troops in the 1857 rebellion?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Colin Campbell</t>
+          <t>Begum Rokeya</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Colin Campbell</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>He led the recapture of Lucknow.</t>
+          <t>She led the revolt in Awadh and resisted British rule.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>After the 1857 revolt, the British introduced:</t>
+          <t>Who among the following called the revolt a ‘sepoy mutiny’?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Queen’s Proclamation</t>
+          <t>R.C. Majumdar</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Judicial system</t>
+          <t>James Mill</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Queen’s Proclamation</t>
+          <t>R.C. Majumdar</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>It promised non-interference in religion and equal protection of law.</t>
+          <t>He considered it a limited military uprising, not a national movement.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Who among the following led the revolt at Gwalior?</t>
+          <t>Which of the following was not a cause of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Discrimination in army</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>High salary of Indian soldiers</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Religious interference</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Annexation policies</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>High salary of Indian soldiers</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>He continued the struggle after Rani Laxmibai's death.</t>
+          <t>Indian soldiers were paid much less than their British counterparts.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 is also known in British records as:</t>
+          <t>Which region did not participate in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mutiny of 1857</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Civil Rebellion</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Indian Freedom War</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sepoy Rebellion</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mutiny of 1857</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Official British term used to minimize its impact.</t>
+          <t>Largely stayed loyal to the British due to local rivalries and Sikh-British cooperation.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What was the main military grievance that triggered the Revolt of 1857?</t>
+          <t>Which of the following social groups was least involved in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lack of promotion</t>
+          <t>Artisans</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Low salary</t>
+          <t>Peasants</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Use of greased cartridges</t>
+          <t>Soldiers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Deployment in Burma</t>
+          <t>Lawyers</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Use of greased cartridges</t>
+          <t>Lawyers</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Cartridges greased with cow/pig fat offended both Hindus and Muslims.</t>
+          <t>They were few and mostly stayed aloof or loyal to the British.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who was declared the symbolic leader of the Revolt of 1857?</t>
+          <t>Who described the revolt as “a war between civilization and barbarism”?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>James Mill</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Winston Churchill</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Thomas Macaulay</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>He was declared the emperor of India by the rebels.</t>
+          <t>British leaders used such language to justify colonialism.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which of the following was promised in the Queen's Proclamation of 1858?</t>
+          <t>Which book describes the Revolt of 1857 as a national revolt?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Right to vote</t>
+          <t>India’s Struggle for Independence</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Equal rights before law</t>
+          <t>The History of the Indian Mutiny</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Complete self-rule</t>
+          <t>The Indian War of Independence</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Independence</t>
+          <t>Discovery of India</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Equal rights before law</t>
+          <t>The Indian War of Independence</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>It tried to pacify Indians and prevent further revolts.</t>
+          <t>Written by V.D. Savarkar glorifying the revolt.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who among the following was hanged in 1859 for his role in the revolt?</t>
+          <t>Who led the revolt in Kanpur?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Nana Sahib</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Rani Laxmibai</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Tantia Tope</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kunwar Singh</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>Nana Sahib</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Bahadur Shah</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Rani Laxmibai</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Tantia Tope</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>He was captured and executed by the British.</t>
+          <t>He led the rebellion after being denied his father's pension.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which British policy was resented by Indian rulers leading up to 1857?</t>
+          <t>Which one of the following was a consequence of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pitt’s India Act</t>
+          <t>Indian National Congress was formed</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Subsidiary Alliance</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Doctrine of Lapse</t>
+          <t>End of Company rule</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Permanent Settlement</t>
+          <t>Beginning of Non-cooperation</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Doctrine of Lapse</t>
+          <t>End of Company rule</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Used to annex several princely states without heirs.</t>
+          <t>The British Crown took direct control over India in 1858.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which of these was not a cause of discontent among Indian soldiers?</t>
+          <t>The 1857 revolt failed largely due to:</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Restriction on caste practices</t>
+          <t>Lack of weapons</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deployment overseas</t>
+          <t>Lack of local support</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Equal pay with British troops</t>
+          <t>Limited area of spread</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Religious interference</t>
+          <t>Strong leadership</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Equal pay with British troops</t>
+          <t>Limited area of spread</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>They were paid **less**, not equally.</t>
+          <t>It did not involve most of South and East India.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which state was annexed by the British on the pretext of misgovernance?</t>
+          <t>What was the result of the revolt of 1857?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>British left India</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Company rule ended</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Satara</t>
+          <t>Indian National Congress formed</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Queen Victoria exiled</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Company rule ended</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Annexed in 1856, seen as an injustice by Indian nobility.</t>
+          <t>The British Crown took direct control over India in 1858.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What was the role of Bahadur Shah Zafar in the revolt?</t>
+          <t>Which of these was not a cause of discontent among Indian soldiers?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Military planner</t>
+          <t>Restriction on caste practices</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Active field commander</t>
+          <t>Deployment overseas</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Symbolic leader</t>
+          <t>Equal pay with British troops</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>British spy</t>
+          <t>Religious interference</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Symbolic leader</t>
+          <t>Equal pay with British troops</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>He was declared the emperor by the rebels, though old and powerless.</t>
+          <t>They were paid **less**, not equally.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Who led the revolt in Kanpur?</t>
+          <t>The term "sepoy mutiny" was mainly used by:</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Nationalist historians</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>British historians</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Marxist historians</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Modern Indian scholars</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>British historians</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>He led the rebellion after being denied his father's pension.</t>
+          <t>They downplayed the revolt’s scale and called it a mere military rebellion.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which famous queen died in battle during the 1857 revolt?</t>
+          <t>Who led the revolt in Bihar during 1857?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rani Velu Nachiyar</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rani Durgavati</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Fought bravely against the British in Gwalior.</t>
+          <t>A zamindar from Jagdishpur who joined the rebellion despite his age.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which ruler's state was annexed under the Doctrine of Lapse, triggering her participation in the 1857 revolt?</t>
+          <t>The Revolt of 1857 was also referred to as:</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Civil War</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>War of Religion</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>First War of Indian Independence</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Sepoy Mutiny</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>First War of Indian Independence</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Her state Jhansi was annexed by the British under the Doctrine of Lapse.</t>
+          <t>Term used by Indian nationalists to honor its significance.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 began from which place?</t>
+          <t>Who led the revolt in Faizabad?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Meerut</t>
+          <t>Bahadur Shah</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barrackpore</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Meerut</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>It started on May 10, 1857, when soldiers mutinied.</t>
+          <t>An influential religious leader who organized local resistance.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which princely state supported the British during the 1857 revolt?</t>
+          <t>The Revolt of 1857 was described as a "feudal outburst" by:</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Bipan Chandra</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>R.C. Majumdar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Karl Marx</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>James Mill</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Karl Marx</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The Nizam of Hyderabad remained loyal to the British.</t>
+          <t>He called it a rebellion of feudal lords against modern capitalism.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which group played a limited role in the revolt of 1857?</t>
+          <t>Which ruler's state was annexed under the Doctrine of Lapse, triggering her participation in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Peasants</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Zamindars</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Princes</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Western-educated Indians</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Western-educated Indians</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>They generally stayed loyal or neutral, as they benefited from British reforms.</t>
+          <t>Her state Jhansi was annexed by the British under the Doctrine of Lapse.</t>
         </is>
       </c>
     </row>
@@ -1672,241 +1672,241 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which book describes the Revolt of 1857 as a national revolt?</t>
+          <t>Which city saw fierce fighting and massacre during the revolt?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>India’s Struggle for Independence</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>The History of the Indian Mutiny</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>The Indian War of Independence</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Discovery of India</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>The Indian War of Independence</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Written by V.D. Savarkar glorifying the revolt.</t>
+          <t>Site of Nana Sahib’s major rebellion and British retaliation.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which one of the following cities was not a major centre of the 1857 revolt?</t>
+          <t>Which act transferred control from the Company to the Crown?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Charter Act 1853</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Regulating Act</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Indian Councils Act</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Southern India remained mostly unaffected by the revolt.</t>
+          <t>Ended the East India Company's rule.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which city saw fierce fighting and massacre during the revolt?</t>
+          <t>What was the role of Bahadur Shah Zafar in the revolt?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Military planner</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Active field commander</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Symbolic leader</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>British spy</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Symbolic leader</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Site of Nana Sahib’s major rebellion and British retaliation.</t>
+          <t>He was declared the emperor by the rebels, though old and powerless.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Which of these regions remained largely unaffected by the revolt?</t>
+          <t>What was the main reason behind the failure of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>British military strength</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Lack of foreign support</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Lack of leadership and unity</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Economic weakness</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Lack of leadership and unity</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Many local rulers, especially Sikhs, supported the British.</t>
+          <t>There was no single coordinated command structure.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which of the following was not a leader in the 1857 revolt?</t>
+          <t>The 1857 revolt is considered the first struggle for independence because:</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>It succeeded</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Rani Gaidinliu</t>
+          <t>It united all classes</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>It had nationalist elements</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>It was supported by INC</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rani Gaidinliu</t>
+          <t>It had nationalist elements</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>She was a Naga leader who resisted the British in the 1930s, not 1857.</t>
+          <t>Though limited, it was the first widespread anti-British effort.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>The 1857 revolt failed largely due to:</t>
+          <t>Who was declared the symbolic leader of the Revolt of 1857?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lack of weapons</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lack of local support</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Limited area of spread</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Strong leadership</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Limited area of spread</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>It did not involve most of South and East India.</t>
+          <t>He was declared the emperor of India by the rebels.</t>
         </is>
       </c>
     </row>
@@ -1952,521 +1952,521 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What was the main reason behind the failure of the 1857 revolt?</t>
+          <t>Who was the British Governor-General during the revolt?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>British military strength</t>
+          <t>Lord Canning</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lack of foreign support</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lack of leadership and unity</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Economic weakness</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lack of leadership and unity</t>
+          <t>Lord Canning</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>There was no single coordinated command structure.</t>
+          <t>He was the last Governor-General of the East India Company and first Viceroy of British India.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What was the result of the revolt of 1857?</t>
+          <t>Which one of these was a British general during the suppression of the revolt?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>British left India</t>
+          <t>Colin Campbell</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Company rule ended</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Indian National Congress formed</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Queen Victoria exiled</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Company rule ended</t>
+          <t>Colin Campbell</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>The British Crown took direct control over India in 1858.</t>
+          <t>He led the recapture of Lucknow.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which act transferred control from the Company to the Crown?</t>
+          <t>After the 1857 revolt, the British introduced:</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charter Act 1853</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Regulating Act</t>
+          <t>Queen’s Proclamation</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Indian Councils Act</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Judicial system</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Queen’s Proclamation</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Ended the East India Company's rule.</t>
+          <t>It promised non-interference in religion and equal protection of law.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Who among the following called the revolt a ‘sepoy mutiny’?</t>
+          <t>Which leader used religious appeal to mobilize people in 1857?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>R.C. Majumdar</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>James Mill</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>R.C. Majumdar</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>He considered it a limited military uprising, not a national movement.</t>
+          <t>He used Islamic preaching to unite fighters in Awadh.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Who captured Delhi back from the rebels in 1857?</t>
+          <t>The immediate cause of the 1857 Revolt was related to:</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Colin Campbell</t>
+          <t>Heavy taxation</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>John Nicholson</t>
+          <t>New land revenue policies</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hugh Rose</t>
+          <t>Greased cartridges</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>Annexation of Awadh</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>John Nicholson</t>
+          <t>Greased cartridges</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Led British troops to recapture Delhi from Indian rebels.</t>
+          <t>The use of animal fat-greased cartridges hurt religious sentiments.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which rebel leader used guerrilla warfare after defeat in open battle?</t>
+          <t>Which of these regions remained largely unaffected by the revolt?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>He used hit-and-run tactics after initial defeats.</t>
+          <t>Many local rulers, especially Sikhs, supported the British.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which leader used religious appeal to mobilize people in 1857?</t>
+          <t>The Revolt of 1857 began from which place?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Meerut</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Barrackpore</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Meerut</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>He used Islamic preaching to unite fighters in Awadh.</t>
+          <t>It started on May 10, 1857, when soldiers mutinied.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Who was the British Governor-General during the revolt?</t>
+          <t>Who among the following was hanged in 1859 for his role in the revolt?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lord Canning</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>Bahadur Shah</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lord Canning</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>He was the last Governor-General of the East India Company and first Viceroy of British India.</t>
+          <t>He was captured and executed by the British.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which of the following pairs is correctly matched?</t>
+          <t>Which of the following was not a leader in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lucknow – Rani Laxmibai</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Kanpur – Tantia Tope</t>
+          <t>Rani Gaidinliu</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Delhi – Bahadur Shah Zafar</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Jhansi – Nana Sahib</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Delhi – Bahadur Shah Zafar</t>
+          <t>Rani Gaidinliu</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>He was declared the emperor in Delhi by the rebels.</t>
+          <t>She was a Naga leader who resisted the British in the 1930s, not 1857.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 was described as a "feudal outburst" by:</t>
+          <t>Who among the following led the revolt at Gwalior?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bipan Chandra</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>R.C. Majumdar</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Karl Marx</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>James Mill</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Karl Marx</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>He called it a rebellion of feudal lords against modern capitalism.</t>
+          <t>He continued the struggle after Rani Laxmibai's death.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which one of the following was a consequence of the 1857 revolt?</t>
+          <t>What was the main military grievance that triggered the Revolt of 1857?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Indian National Congress was formed</t>
+          <t>Lack of promotion</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>Low salary</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>End of Company rule</t>
+          <t>Use of greased cartridges</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Beginning of Non-cooperation</t>
+          <t>Deployment in Burma</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>End of Company rule</t>
+          <t>Use of greased cartridges</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>The British Crown took direct control over India in 1858.</t>
+          <t>Cartridges greased with cow/pig fat offended both Hindus and Muslims.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The immediate cause of the 1857 Revolt was related to:</t>
+          <t>Which British policy was resented by Indian rulers leading up to 1857?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Heavy taxation</t>
+          <t>Pitt’s India Act</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>New land revenue policies</t>
+          <t>Subsidiary Alliance</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Greased cartridges</t>
+          <t>Doctrine of Lapse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Annexation of Awadh</t>
+          <t>Permanent Settlement</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Greased cartridges</t>
+          <t>Doctrine of Lapse</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>The use of animal fat-greased cartridges hurt religious sentiments.</t>
+          <t>Used to annex several princely states without heirs.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which of the following social groups was least involved in the 1857 revolt?</t>
+          <t>The Revolt of 1857 is also known in British records as:</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Artisans</t>
+          <t>Mutiny of 1857</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Peasants</t>
+          <t>Civil Rebellion</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Soldiers</t>
+          <t>Indian Freedom War</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lawyers</t>
+          <t>Sepoy Rebellion</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lawyers</t>
+          <t>Mutiny of 1857</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>They were few and mostly stayed aloof or loyal to the British.</t>
+          <t>Official British term used to minimize its impact.</t>
         </is>
       </c>
     </row>

--- a/Data/MH_TheRevolt.xlsx
+++ b/Data/MH_TheRevolt.xlsx
@@ -472,801 +472,801 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which princely state supported the British during the 1857 revolt?</t>
+          <t>Which leader used religious appeal to mobilize people in 1857?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Maulvi Ahmadullah Shah</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The Nizam of Hyderabad remained loyal to the British.</t>
+          <t>He used Islamic preaching to unite fighters in Awadh.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which of the following was promised in the Queen's Proclamation of 1858?</t>
+          <t>The immediate cause of the 1857 Revolt was related to:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Right to vote</t>
+          <t>Heavy taxation</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Equal rights before law</t>
+          <t>New land revenue policies</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Complete self-rule</t>
+          <t>Greased cartridges</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Independence</t>
+          <t>Annexation of Awadh</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Equal rights before law</t>
+          <t>Greased cartridges</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>It tried to pacify Indians and prevent further revolts.</t>
+          <t>The use of animal fat-greased cartridges hurt religious sentiments.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Who captured Delhi back from the rebels in 1857?</t>
+          <t>Which of these regions remained largely unaffected by the revolt?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Colin Campbell</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>John Nicholson</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hugh Rose</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>John Nicholson</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Led British troops to recapture Delhi from Indian rebels.</t>
+          <t>Many local rulers, especially Sikhs, supported the British.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which state was annexed by the British on the pretext of misgovernance?</t>
+          <t>The Revolt of 1857 began from which place?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Meerut</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Satara</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Barrackpore</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Meerut</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Annexed in 1856, seen as an injustice by Indian nobility.</t>
+          <t>It started on May 10, 1857, when soldiers mutinied.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which rebel leader used guerrilla warfare after defeat in open battle?</t>
+          <t>Who among the following was hanged in 1859 for his role in the revolt?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>Tantia Tope</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>Nana Sahib</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Kunwar Singh</t>
-        </is>
-      </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Bahadur Shah</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rani Laxmibai</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>Tantia Tope</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Rani Laxmibai</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Tantia Tope</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>He used hit-and-run tactics after initial defeats.</t>
+          <t>He was captured and executed by the British.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which of the following best describes the nature of the 1857 revolt?</t>
+          <t>Which of the following was not a leader in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Only military</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Only peasant-based</t>
+          <t>Rani Gaidinliu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Regional uprising</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Combination of political, social, and military causes</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Combination of political, social, and military causes</t>
+          <t>Rani Gaidinliu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Multiple classes were involved for various reasons.</t>
+          <t>She was a Naga leader who resisted the British in the 1930s, not 1857.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which group played a limited role in the revolt of 1857?</t>
+          <t>Who among the following led the revolt at Gwalior?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Peasants</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Zamindars</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Princes</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Western-educated Indians</t>
+          <t>Kunwar Singh</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Western-educated Indians</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>They generally stayed loyal or neutral, as they benefited from British reforms.</t>
+          <t>He continued the struggle after Rani Laxmibai's death.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Who was the first martyr of the 1857 revolt?</t>
+          <t>What was the main military grievance that triggered the Revolt of 1857?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Lack of promotion</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Low salary</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Use of greased cartridges</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Deployment in Burma</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mangal Pandey</t>
+          <t>Use of greased cartridges</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>He attacked British officers at Barrackpore.</t>
+          <t>Cartridges greased with cow/pig fat offended both Hindus and Muslims.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which one of the following cities was not a major centre of the 1857 revolt?</t>
+          <t>Which British policy was resented by Indian rulers leading up to 1857?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Pitt’s India Act</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Subsidiary Alliance</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Doctrine of Lapse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Permanent Settlement</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Madras</t>
+          <t>Doctrine of Lapse</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Southern India remained mostly unaffected by the revolt.</t>
+          <t>Used to annex several princely states without heirs.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which famous queen died in battle during the 1857 revolt?</t>
+          <t>The Revolt of 1857 is also known in British records as:</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rani Velu Nachiyar</t>
+          <t>Mutiny of 1857</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Civil Rebellion</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Indian Freedom War</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rani Durgavati</t>
+          <t>Sepoy Rebellion</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Mutiny of 1857</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fought bravely against the British in Gwalior.</t>
+          <t>Official British term used to minimize its impact.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which of the following pairs is correctly matched?</t>
+          <t>Which city saw fierce fighting and massacre during the revolt?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lucknow – Rani Laxmibai</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Kanpur – Tantia Tope</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Delhi – Bahadur Shah Zafar</t>
+          <t>Amritsar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jhansi – Nana Sahib</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Delhi – Bahadur Shah Zafar</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>He was declared the emperor in Delhi by the rebels.</t>
+          <t>Site of Nana Sahib’s major rebellion and British retaliation.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which female leader actively led troops in the 1857 rebellion?</t>
+          <t>Which act transferred control from the Company to the Crown?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Begum Rokeya</t>
+          <t>Charter Act 1853</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Annie Besant</t>
+          <t>Regulating Act</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Indian Councils Act</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sarojini Naidu</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Begum Hazrat Mahal</t>
+          <t>Government of India Act 1858</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>She led the revolt in Awadh and resisted British rule.</t>
+          <t>Ended the East India Company's rule.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Who among the following called the revolt a ‘sepoy mutiny’?</t>
+          <t>What was the role of Bahadur Shah Zafar in the revolt?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jawaharlal Nehru</t>
+          <t>Military planner</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>R.C. Majumdar</t>
+          <t>Active field commander</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>Symbolic leader</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>James Mill</t>
+          <t>British spy</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>R.C. Majumdar</t>
+          <t>Symbolic leader</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>He considered it a limited military uprising, not a national movement.</t>
+          <t>He was declared the emperor by the rebels, though old and powerless.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which of the following was not a cause of the 1857 revolt?</t>
+          <t>What was the main reason behind the failure of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Discrimination in army</t>
+          <t>British military strength</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>High salary of Indian soldiers</t>
+          <t>Lack of foreign support</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Religious interference</t>
+          <t>Lack of leadership and unity</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Annexation policies</t>
+          <t>Economic weakness</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>High salary of Indian soldiers</t>
+          <t>Lack of leadership and unity</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Indian soldiers were paid much less than their British counterparts.</t>
+          <t>There was no single coordinated command structure.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which region did not participate in the 1857 revolt?</t>
+          <t>The 1857 revolt is considered the first struggle for independence because:</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>It succeeded</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>It united all classes</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>It had nationalist elements</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jhansi</t>
+          <t>It was supported by INC</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>It had nationalist elements</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Largely stayed loyal to the British due to local rivalries and Sikh-British cooperation.</t>
+          <t>Though limited, it was the first widespread anti-British effort.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which of the following social groups was least involved in the 1857 revolt?</t>
+          <t>Who was declared the symbolic leader of the Revolt of 1857?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Artisans</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Peasants</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Soldiers</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lawyers</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lawyers</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>They were few and mostly stayed aloof or loyal to the British.</t>
+          <t>He was declared the emperor of India by the rebels.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Who described the revolt as “a war between civilization and barbarism”?</t>
+          <t>Which of the following was a social cause of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>James Mill</t>
+          <t>Ban on widow remarriage</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>Introduction of western education</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Winston Churchill</t>
+          <t>Sati abolition</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomas Macaulay</t>
+          <t>Religious interference by British</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Benjamin Disraeli</t>
+          <t>Religious interference by British</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>British leaders used such language to justify colonialism.</t>
+          <t>Missionary activities and law reforms hurt native sentiments.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which book describes the Revolt of 1857 as a national revolt?</t>
+          <t>Who was the British Governor-General during the revolt?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>India’s Struggle for Independence</t>
+          <t>Lord Canning</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>The History of the Indian Mutiny</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>The Indian War of Independence</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Discovery of India</t>
+          <t>Lord Curzon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>The Indian War of Independence</t>
+          <t>Lord Canning</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Written by V.D. Savarkar glorifying the revolt.</t>
+          <t>He was the last Governor-General of the East India Company and first Viceroy of British India.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who led the revolt in Kanpur?</t>
+          <t>Which one of these was a British general during the suppression of the revolt?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>Colin Campbell</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tantia Tope</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>Nana Sahib</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Rani Laxmibai</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Tantia Tope</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Lord Ripon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Colin Campbell</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>He led the rebellion after being denied his father's pension.</t>
+          <t>He led the recapture of Lucknow.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which one of the following was a consequence of the 1857 revolt?</t>
+          <t>After the 1857 revolt, the British introduced:</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Indian National Congress was formed</t>
+          <t>Railways</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>Queen’s Proclamation</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>Partition of Bengal</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>End of Company rule</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Beginning of Non-cooperation</t>
+          <t>Judicial system</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>End of Company rule</t>
+          <t>Queen’s Proclamation</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The British Crown took direct control over India in 1858.</t>
+          <t>It promised non-interference in religion and equal protection of law.</t>
         </is>
       </c>
     </row>
@@ -1672,588 +1672,588 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which city saw fierce fighting and massacre during the revolt?</t>
+          <t>Which of the following pairs is correctly matched?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Lucknow – Rani Laxmibai</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Kanpur – Tantia Tope</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amritsar</t>
+          <t>Delhi – Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Jhansi – Nana Sahib</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Delhi – Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Site of Nana Sahib’s major rebellion and British retaliation.</t>
+          <t>He was declared the emperor in Delhi by the rebels.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which act transferred control from the Company to the Crown?</t>
+          <t>Which female leader actively led troops in the 1857 rebellion?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charter Act 1853</t>
+          <t>Begum Rokeya</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Regulating Act</t>
+          <t>Annie Besant</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Indian Councils Act</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Sarojini Naidu</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Government of India Act 1858</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Ended the East India Company's rule.</t>
+          <t>She led the revolt in Awadh and resisted British rule.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What was the role of Bahadur Shah Zafar in the revolt?</t>
+          <t>Who among the following called the revolt a ‘sepoy mutiny’?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Military planner</t>
+          <t>Jawaharlal Nehru</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Active field commander</t>
+          <t>R.C. Majumdar</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Symbolic leader</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>British spy</t>
+          <t>James Mill</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Symbolic leader</t>
+          <t>R.C. Majumdar</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>He was declared the emperor by the rebels, though old and powerless.</t>
+          <t>He considered it a limited military uprising, not a national movement.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What was the main reason behind the failure of the 1857 revolt?</t>
+          <t>Which of the following was not a cause of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>British military strength</t>
+          <t>Discrimination in army</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lack of foreign support</t>
+          <t>High salary of Indian soldiers</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lack of leadership and unity</t>
+          <t>Religious interference</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Economic weakness</t>
+          <t>Annexation policies</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lack of leadership and unity</t>
+          <t>High salary of Indian soldiers</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>There was no single coordinated command structure.</t>
+          <t>Indian soldiers were paid much less than their British counterparts.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The 1857 revolt is considered the first struggle for independence because:</t>
+          <t>Which region did not participate in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>It succeeded</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>It united all classes</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>It had nationalist elements</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>It was supported by INC</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>It had nationalist elements</t>
+          <t>Punjab</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Though limited, it was the first widespread anti-British effort.</t>
+          <t>Largely stayed loyal to the British due to local rivalries and Sikh-British cooperation.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who was declared the symbolic leader of the Revolt of 1857?</t>
+          <t>Which of the following social groups was least involved in the 1857 revolt?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Artisans</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Peasants</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Soldiers</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Lawyers</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Lawyers</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>He was declared the emperor of India by the rebels.</t>
+          <t>They were few and mostly stayed aloof or loyal to the British.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which of the following was a social cause of the 1857 revolt?</t>
+          <t>Who described the revolt as “a war between civilization and barbarism”?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ban on widow remarriage</t>
+          <t>James Mill</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Introduction of western education</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sati abolition</t>
+          <t>Winston Churchill</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Religious interference by British</t>
+          <t>Thomas Macaulay</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Religious interference by British</t>
+          <t>Benjamin Disraeli</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Missionary activities and law reforms hurt native sentiments.</t>
+          <t>British leaders used such language to justify colonialism.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Who was the British Governor-General during the revolt?</t>
+          <t>Which book describes the Revolt of 1857 as a national revolt?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lord Canning</t>
+          <t>India’s Struggle for Independence</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lord Dalhousie</t>
+          <t>The History of the Indian Mutiny</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Lord Ripon</t>
+          <t>The Indian War of Independence</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lord Curzon</t>
+          <t>Discovery of India</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lord Canning</t>
+          <t>The Indian War of Independence</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>He was the last Governor-General of the East India Company and first Viceroy of British India.</t>
+          <t>Written by V.D. Savarkar glorifying the revolt.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which one of these was a British general during the suppression of the revolt?</t>
+          <t>Who led the revolt in Kanpur?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Colin Campbell</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>Rani Laxmibai</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>Tantia Tope</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Kunwar Singh</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>Nana Sahib</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Lord Ripon</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Colin Campbell</t>
-        </is>
-      </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>He led the recapture of Lucknow.</t>
+          <t>He led the rebellion after being denied his father's pension.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>After the 1857 revolt, the British introduced:</t>
+          <t>Which one of the following was a consequence of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Railways</t>
+          <t>Indian National Congress was formed</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Queen’s Proclamation</t>
+          <t>Partition of Bengal</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Partition of Bengal</t>
+          <t>End of Company rule</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Judicial system</t>
+          <t>Beginning of Non-cooperation</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Queen’s Proclamation</t>
+          <t>End of Company rule</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>It promised non-interference in religion and equal protection of law.</t>
+          <t>The British Crown took direct control over India in 1858.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which leader used religious appeal to mobilize people in 1857?</t>
+          <t>Which princely state supported the British during the 1857 revolt?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Maulvi Ahmadullah Shah</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>He used Islamic preaching to unite fighters in Awadh.</t>
+          <t>The Nizam of Hyderabad remained loyal to the British.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The immediate cause of the 1857 Revolt was related to:</t>
+          <t>Which of the following was promised in the Queen's Proclamation of 1858?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Heavy taxation</t>
+          <t>Right to vote</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>New land revenue policies</t>
+          <t>Equal rights before law</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Greased cartridges</t>
+          <t>Complete self-rule</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Annexation of Awadh</t>
+          <t>Independence</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Greased cartridges</t>
+          <t>Equal rights before law</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>The use of animal fat-greased cartridges hurt religious sentiments.</t>
+          <t>It tried to pacify Indians and prevent further revolts.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which of these regions remained largely unaffected by the revolt?</t>
+          <t>Who captured Delhi back from the rebels in 1857?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Awadh</t>
+          <t>Colin Campbell</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>John Nicholson</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>Hugh Rose</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Lord Dalhousie</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Punjab</t>
+          <t>John Nicholson</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Many local rulers, especially Sikhs, supported the British.</t>
+          <t>Led British troops to recapture Delhi from Indian rebels.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 began from which place?</t>
+          <t>Which state was annexed by the British on the pretext of misgovernance?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Jhansi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Meerut</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kanpur</t>
+          <t>Satara</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barrackpore</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Meerut</t>
+          <t>Awadh</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>It started on May 10, 1857, when soldiers mutinied.</t>
+          <t>Annexed in 1856, seen as an injustice by Indian nobility.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Who among the following was hanged in 1859 for his role in the revolt?</t>
+          <t>Which rebel leader used guerrilla warfare after defeat in open battle?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
+          <t>Nana Sahib</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Kunwar Singh</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>Tantia Tope</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Nana Sahib</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Bahadur Shah</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>Rani Laxmibai</t>
@@ -2266,207 +2266,207 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>He was captured and executed by the British.</t>
+          <t>He used hit-and-run tactics after initial defeats.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which of the following was not a leader in the 1857 revolt?</t>
+          <t>Which of the following best describes the nature of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bahadur Shah Zafar</t>
+          <t>Only military</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Rani Gaidinliu</t>
+          <t>Only peasant-based</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Regional uprising</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Combination of political, social, and military causes</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rani Gaidinliu</t>
+          <t>Combination of political, social, and military causes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>She was a Naga leader who resisted the British in the 1930s, not 1857.</t>
+          <t>Multiple classes were involved for various reasons.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Who among the following led the revolt at Gwalior?</t>
+          <t>Which group played a limited role in the revolt of 1857?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Rani Laxmibai</t>
+          <t>Peasants</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Nana Sahib</t>
+          <t>Zamindars</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Princes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kunwar Singh</t>
+          <t>Western-educated Indians</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tantia Tope</t>
+          <t>Western-educated Indians</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>He continued the struggle after Rani Laxmibai's death.</t>
+          <t>They generally stayed loyal or neutral, as they benefited from British reforms.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What was the main military grievance that triggered the Revolt of 1857?</t>
+          <t>Who was the first martyr of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lack of promotion</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Low salary</t>
+          <t>Tantia Tope</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Use of greased cartridges</t>
+          <t>Bahadur Shah Zafar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Deployment in Burma</t>
+          <t>Nana Sahib</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Use of greased cartridges</t>
+          <t>Mangal Pandey</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Cartridges greased with cow/pig fat offended both Hindus and Muslims.</t>
+          <t>He attacked British officers at Barrackpore.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which British policy was resented by Indian rulers leading up to 1857?</t>
+          <t>Which one of the following cities was not a major centre of the 1857 revolt?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pitt’s India Act</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Subsidiary Alliance</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Doctrine of Lapse</t>
+          <t>Madras</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Permanent Settlement</t>
+          <t>Kanpur</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Doctrine of Lapse</t>
+          <t>Madras</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Used to annex several princely states without heirs.</t>
+          <t>Southern India remained mostly unaffected by the revolt.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>The Revolt of 1857 is also known in British records as:</t>
+          <t>Which famous queen died in battle during the 1857 revolt?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mutiny of 1857</t>
+          <t>Rani Velu Nachiyar</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Civil Rebellion</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Indian Freedom War</t>
+          <t>Begum Hazrat Mahal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sepoy Rebellion</t>
+          <t>Rani Durgavati</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Mutiny of 1857</t>
+          <t>Rani Laxmibai</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Official British term used to minimize its impact.</t>
+          <t>Fought bravely against the British in Gwalior.</t>
         </is>
       </c>
     </row>
